--- a/EspectrosSismo_Naves_ElSalvador_NTDS_ASCE_STAAD_R2.8.xlsx
+++ b/EspectrosSismo_Naves_ElSalvador_NTDS_ASCE_STAAD_R2.8.xlsx
@@ -12100,14 +12100,14 @@
         <v>170</v>
       </c>
       <c r="C60" s="15">
-        <v>15.55</v>
+        <v>17.49</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>171</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>CAPTURA. De AreasTributarias_NOSE_DOCK_H5_H6_R2.8.xlsx, hoja RESUMEN: acero 9.88 t + CM techo 3.12 t + CM muros 2.15 t + cortina 0.40 t + w_i = 0 (pendiente &gt; 5%) = 15.55 t. Compáralo con la suma de cargas del caso 1 en STAAD.</t>
+          <t>CAPTURA. De AreasTributarias_NOSE_DOCK_H5_H6_R2.8.xlsx, hoja RESUMEN: acero 11.82 t + CM techo 3.12 t + CM muros 2.15 t + cortina 0.40 t + w_i = 0 (pendiente &gt; 5%) = 17.49 t. Compáralo con la suma de cargas del caso 1 en STAAD.</t>
         </is>
       </c>
       <c r="F60" s="4" t="s">
@@ -12119,14 +12119,14 @@
         <v>174</v>
       </c>
       <c r="C61" s="15">
-        <v>15.55</v>
+        <v>17.49</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>171</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>CAPTURA. CM sin almacenamiento, particiones ni equipo permanente: igual que la NTDS, 15.55 t (fuera del AMSS sólo es referencia).</t>
+          <t>CAPTURA. CM sin almacenamiento, particiones ni equipo permanente: igual que la NTDS, 17.49 t (fuera del AMSS sólo es referencia).</t>
         </is>
       </c>
       <c r="F61" s="4" t="s">
@@ -12681,11 +12681,11 @@
       </c>
       <c r="C24" s="21">
         <f>$C$23*DATOS!$C$60</f>
-        <v>3.19885714285714</v>
+        <v>3.59794285714286</v>
       </c>
       <c r="D24" s="21">
         <f>$D$23*DATOS!$C$60</f>
-        <v>3.19885714285714</v>
+        <v>3.59794285714286</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>171</v>
@@ -13228,11 +13228,11 @@
       </c>
       <c r="C51" s="21">
         <f>$C$50*DATOS!$C$61</f>
-        <v>7.59313904761905</v>
+        <v>8.54045028571428</v>
       </c>
       <c r="D51" s="21">
         <f>$D$50*DATOS!$C$61</f>
-        <v>7.59313904761905</v>
+        <v>8.54045028571428</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>171</v>
@@ -13379,11 +13379,11 @@
       </c>
       <c r="C60" s="13">
         <f>$C$24*DATOS!$C$12</f>
-        <v>4.57436571428571</v>
+        <v>5.14505828571429</v>
       </c>
       <c r="D60" s="13">
         <f>$D$24*DATOS!$C$12</f>
-        <v>4.57436571428571</v>
+        <v>5.14505828571429</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>171</v>
@@ -13401,11 +13401,11 @@
       </c>
       <c r="C61" s="13">
         <f>$C$51</f>
-        <v>7.59313904761905</v>
+        <v>8.54045028571428</v>
       </c>
       <c r="D61" s="13">
         <f>$D$51</f>
-        <v>7.59313904761905</v>
+        <v>8.54045028571428</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>171</v>
@@ -20878,11 +20878,11 @@
       </c>
       <c r="C9" s="21">
         <f>COEFICIENTE!$C$24</f>
-        <v>3.19885714285714</v>
+        <v>3.59794285714286</v>
       </c>
       <c r="D9" s="21">
         <f>COEFICIENTE!$D$24</f>
-        <v>3.19885714285714</v>
+        <v>3.59794285714286</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>171</v>
@@ -20901,11 +20901,11 @@
       </c>
       <c r="C10" s="7">
         <f>COEFICIENTE!$C$24*9.80665</f>
-        <v>31.3700724</v>
+        <v>35.28376632</v>
       </c>
       <c r="D10" s="7">
         <f>COEFICIENTE!$D$24*9.80665</f>
-        <v>31.3700724</v>
+        <v>35.28376632</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>345</v>
@@ -20947,11 +20947,11 @@
       </c>
       <c r="C12" s="13">
         <f>COEFICIENTE!$C$27*DATOS!$C$60</f>
-        <v>2.87897142857143</v>
+        <v>3.23814857142857</v>
       </c>
       <c r="D12" s="13">
         <f>COEFICIENTE!$D$27*DATOS!$C$60</f>
-        <v>2.87897142857143</v>
+        <v>3.23814857142857</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>171</v>
@@ -20993,11 +20993,11 @@
       </c>
       <c r="C14" s="13">
         <f>COEFICIENTE!$C$51</f>
-        <v>7.59313904761905</v>
+        <v>8.54045028571428</v>
       </c>
       <c r="D14" s="13">
         <f>COEFICIENTE!$D$51</f>
-        <v>7.59313904761905</v>
+        <v>8.54045028571428</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>171</v>
@@ -21016,11 +21016,11 @@
       </c>
       <c r="C15" s="13">
         <f>COEFICIENTE!$C$54*DATOS!$C$61*IF(DATOS!$C$9="SÍ",COEFICIENTE!$C$64,1)</f>
-        <v>7.59313904761905</v>
+        <v>8.54045028571428</v>
       </c>
       <c r="D15" s="13">
         <f>COEFICIENTE!$D$54*DATOS!$C$61*IF(DATOS!$C$9="SÍ",COEFICIENTE!$D$64,1)</f>
-        <v>7.59313904761905</v>
+        <v>8.54045028571428</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>171</v>
@@ -22062,11 +22062,11 @@
       </c>
       <c r="O15" s="21">
         <f>IF(STAAD!$C$17="ASCE 7-16",STAAD!$C$15,STAAD!$C$12)</f>
-        <v>2.87897142857143</v>
+        <v>3.23814857142857</v>
       </c>
       <c r="P15" s="21">
         <f>IF(STAAD!$C$17="ASCE 7-16",STAAD!$D$15,STAAD!$D$12)</f>
-        <v>2.87897142857143</v>
+        <v>3.23814857142857</v>
       </c>
       <c r="Q15" s="6" t="s">
         <v>171</v>
